--- a/2fe6ad6e-ec55-4fa5-8a11-6d5a56472b1e/reports/还款核对报告_2026-05.xlsx
+++ b/2fe6ad6e-ec55-4fa5-8a11-6d5a56472b1e/reports/还款核对报告_2026-05.xlsx
@@ -399,21 +399,1707 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>提示</v>
+        <v>银行</v>
+      </c>
+      <c r="B1" t="str">
+        <v>合同号</v>
+      </c>
+      <c r="C1" t="str">
+        <v>借款人</v>
+      </c>
+      <c r="D1" t="str">
+        <v>期次</v>
+      </c>
+      <c r="E1" t="str">
+        <v>异常类型</v>
+      </c>
+      <c r="F1" t="str">
+        <v>应还金额</v>
+      </c>
+      <c r="G1" t="str">
+        <v>实还金额</v>
+      </c>
+      <c r="H1" t="str">
+        <v>应还日期</v>
+      </c>
+      <c r="I1" t="str">
+        <v>实还日期</v>
+      </c>
+      <c r="J1" t="str">
+        <v>逾期天数</v>
+      </c>
+      <c r="K1" t="str">
+        <v>罚息金额</v>
+      </c>
+      <c r="L1" t="str">
+        <v>说明</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>本期无异常</v>
+        <v>CMBC</v>
+      </c>
+      <c r="B2" t="str">
+        <v>AJ-2024-0002</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F2">
+        <v>5800</v>
+      </c>
+      <c r="G2">
+        <v>5800</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>2.17</v>
+      </c>
+      <c r="L2" t="str">
+        <v>逾期 4 天，应还 5800 元，实还 5800 元，罚息 2.17 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BOC</v>
+      </c>
+      <c r="B3" t="str">
+        <v>AJ-2024-0002</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F3">
+        <v>5800</v>
+      </c>
+      <c r="G3">
+        <v>5800</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>2.17</v>
+      </c>
+      <c r="L3" t="str">
+        <v>逾期 4 天，应还 5800 元，实还 5800 元，罚息 2.17 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CMBC</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AJ-2024-0003</v>
+      </c>
+      <c r="C4" t="str">
+        <v>”</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="str">
+        <v>partial</v>
+      </c>
+      <c r="F4">
+        <v>3700</v>
+      </c>
+      <c r="G4">
+        <v>3500</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4" t="str">
+        <v>部分还款，应还 3700 元，实还 3500 元，差额 200 元</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>BOC</v>
+      </c>
+      <c r="B5" t="str">
+        <v>AJ-2024-0003</v>
+      </c>
+      <c r="C5" t="str">
+        <v>”</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="str">
+        <v>partial</v>
+      </c>
+      <c r="F5">
+        <v>3700</v>
+      </c>
+      <c r="G5">
+        <v>3500</v>
+      </c>
+      <c r="H5" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5" t="str">
+        <v>部分还款，应还 3700 元，实还 3500 元，差额 200 元</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CMBC</v>
+      </c>
+      <c r="B6" t="str">
+        <v>AJ-2024-0004</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ł›</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="str">
+        <v>early</v>
+      </c>
+      <c r="F6">
+        <v>7000</v>
+      </c>
+      <c r="G6">
+        <v>12600</v>
+      </c>
+      <c r="H6" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="I6" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" t="str">
+        <v>提前还款，实还 12600 元超出应还 7000 元（合同标记提前结清）</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>BOC</v>
+      </c>
+      <c r="B7" t="str">
+        <v>AJ-2024-0004</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Ł›</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="str">
+        <v>early</v>
+      </c>
+      <c r="F7">
+        <v>7000</v>
+      </c>
+      <c r="G7">
+        <v>12600</v>
+      </c>
+      <c r="H7" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="I7" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" t="str">
+        <v>提前还款，实还 12600 元超出应还 7000 元（合同标记提前结清）</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CMBC</v>
+      </c>
+      <c r="B8" t="str">
+        <v>AJ-2024-0007</v>
+      </c>
+      <c r="C8" t="str">
+        <v>¤„</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F8">
+        <v>6100</v>
+      </c>
+      <c r="G8">
+        <v>6100</v>
+      </c>
+      <c r="H8" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="I8" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8">
+        <v>2.28</v>
+      </c>
+      <c r="L8" t="str">
+        <v>逾期 4 天，应还 6100 元，实还 6100 元，罚息 2.28 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>BOC</v>
+      </c>
+      <c r="B9" t="str">
+        <v>AJ-2024-0007</v>
+      </c>
+      <c r="C9" t="str">
+        <v>¤„</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F9">
+        <v>6100</v>
+      </c>
+      <c r="G9">
+        <v>6100</v>
+      </c>
+      <c r="H9" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="I9" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="J9">
+        <v>4</v>
+      </c>
+      <c r="K9">
+        <v>2.28</v>
+      </c>
+      <c r="L9" t="str">
+        <v>逾期 4 天，应还 6100 元，实还 6100 元，罚息 2.28 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CMBC</v>
+      </c>
+      <c r="B10" t="str">
+        <v>AJ-2024-0008</v>
+      </c>
+      <c r="C10" t="str">
+        <v>·</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="str">
+        <v>unmatched</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10" t="str">
+        <v>未找到应还计划: 合同号=AJ-2024-0008 期次=1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>BOC</v>
+      </c>
+      <c r="B11" t="str">
+        <v>AJ-2024-0008</v>
+      </c>
+      <c r="C11" t="str">
+        <v>·</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="str">
+        <v>unmatched</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11" t="str">
+        <v>未找到应还计划: 合同号=AJ-2024-0008 期次=1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CCB</v>
+      </c>
+      <c r="B12" t="str">
+        <v>AJ-2024-0002</v>
+      </c>
+      <c r="C12" t="str">
+        <v>李四</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F12">
+        <v>5800</v>
+      </c>
+      <c r="G12">
+        <v>5800</v>
+      </c>
+      <c r="H12" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I12" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="J12">
+        <v>4</v>
+      </c>
+      <c r="K12">
+        <v>2.17</v>
+      </c>
+      <c r="L12" t="str">
+        <v>逾期 4 天，应还 5800 元，实还 5800 元，罚息 2.17 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CMB</v>
+      </c>
+      <c r="B13" t="str">
+        <v>AJ-2024-0002</v>
+      </c>
+      <c r="C13" t="str">
+        <v>李四</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F13">
+        <v>5800</v>
+      </c>
+      <c r="G13">
+        <v>5800</v>
+      </c>
+      <c r="H13" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I13" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="J13">
+        <v>4</v>
+      </c>
+      <c r="K13">
+        <v>2.17</v>
+      </c>
+      <c r="L13" t="str">
+        <v>逾期 4 天，应还 5800 元，实还 5800 元，罚息 2.17 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>ICBC</v>
+      </c>
+      <c r="B14" t="str">
+        <v>AJ-2024-0002</v>
+      </c>
+      <c r="C14" t="str">
+        <v>李四</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F14">
+        <v>5800</v>
+      </c>
+      <c r="G14">
+        <v>5800</v>
+      </c>
+      <c r="H14" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I14" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="J14">
+        <v>4</v>
+      </c>
+      <c r="K14">
+        <v>2.17</v>
+      </c>
+      <c r="L14" t="str">
+        <v>逾期 4 天，应还 5800 元，实还 5800 元，罚息 2.17 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SPDB</v>
+      </c>
+      <c r="B15" t="str">
+        <v>AJ-2024-0002</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F15">
+        <v>5800</v>
+      </c>
+      <c r="G15">
+        <v>5800</v>
+      </c>
+      <c r="H15" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I15" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="J15">
+        <v>4</v>
+      </c>
+      <c r="K15">
+        <v>2.17</v>
+      </c>
+      <c r="L15" t="str">
+        <v>逾期 4 天，应还 5800 元，实还 5800 元，罚息 2.17 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>ABC</v>
+      </c>
+      <c r="B16" t="str">
+        <v>AJ-2024-0002</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F16">
+        <v>5800</v>
+      </c>
+      <c r="G16">
+        <v>5800</v>
+      </c>
+      <c r="H16" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I16" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="J16">
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <v>2.17</v>
+      </c>
+      <c r="L16" t="str">
+        <v>逾期 4 天，应还 5800 元，实还 5800 元，罚息 2.17 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>COMM</v>
+      </c>
+      <c r="B17" t="str">
+        <v>AJ-2024-0002</v>
+      </c>
+      <c r="C17" t="str">
+        <v>李四</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F17">
+        <v>5800</v>
+      </c>
+      <c r="G17">
+        <v>5800</v>
+      </c>
+      <c r="H17" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I17" t="str">
+        <v>2026-05-24</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="K17">
+        <v>2.17</v>
+      </c>
+      <c r="L17" t="str">
+        <v>逾期 4 天，应还 5800 元，实还 5800 元，罚息 2.17 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CCB</v>
+      </c>
+      <c r="B18" t="str">
+        <v>AJ-2024-0003</v>
+      </c>
+      <c r="C18" t="str">
+        <v>王五</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="str">
+        <v>partial</v>
+      </c>
+      <c r="F18">
+        <v>3700</v>
+      </c>
+      <c r="G18">
+        <v>3500</v>
+      </c>
+      <c r="H18" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="I18" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18" t="str">
+        <v>部分还款，应还 3700 元，实还 3500 元，差额 200 元</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CMB</v>
+      </c>
+      <c r="B19" t="str">
+        <v>AJ-2024-0003</v>
+      </c>
+      <c r="C19" t="str">
+        <v>王五</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="str">
+        <v>partial</v>
+      </c>
+      <c r="F19">
+        <v>3700</v>
+      </c>
+      <c r="G19">
+        <v>3500</v>
+      </c>
+      <c r="H19" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="I19" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" t="str">
+        <v>部分还款，应还 3700 元，实还 3500 元，差额 200 元</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>ICBC</v>
+      </c>
+      <c r="B20" t="str">
+        <v>AJ-2024-0003</v>
+      </c>
+      <c r="C20" t="str">
+        <v>王五</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="str">
+        <v>partial</v>
+      </c>
+      <c r="F20">
+        <v>3700</v>
+      </c>
+      <c r="G20">
+        <v>3500</v>
+      </c>
+      <c r="H20" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="I20" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20" t="str">
+        <v>部分还款，应还 3700 元，实还 3500 元，差额 200 元</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>COMM</v>
+      </c>
+      <c r="B21" t="str">
+        <v>AJ-2024-0003</v>
+      </c>
+      <c r="C21" t="str">
+        <v>王五</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="str">
+        <v>partial</v>
+      </c>
+      <c r="F21">
+        <v>3700</v>
+      </c>
+      <c r="G21">
+        <v>3500</v>
+      </c>
+      <c r="H21" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="I21" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21" t="str">
+        <v>部分还款，应还 3700 元，实还 3500 元，差额 200 元</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SPDB</v>
+      </c>
+      <c r="B22" t="str">
+        <v>AJ-2024-0003</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="str">
+        <v>partial</v>
+      </c>
+      <c r="F22">
+        <v>3700</v>
+      </c>
+      <c r="G22">
+        <v>3500</v>
+      </c>
+      <c r="H22" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="I22" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22" t="str">
+        <v>部分还款，应还 3700 元，实还 3500 元，差额 200 元</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>ABC</v>
+      </c>
+      <c r="B23" t="str">
+        <v>AJ-2024-0003</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="str">
+        <v>partial</v>
+      </c>
+      <c r="F23">
+        <v>3700</v>
+      </c>
+      <c r="G23">
+        <v>3500</v>
+      </c>
+      <c r="H23" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="I23" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23" t="str">
+        <v>部分还款，应还 3700 元，实还 3500 元，差额 200 元</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>CCB</v>
+      </c>
+      <c r="B24" t="str">
+        <v>AJ-2024-0004</v>
+      </c>
+      <c r="C24" t="str">
+        <v>赵六</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="str">
+        <v>early</v>
+      </c>
+      <c r="F24">
+        <v>7000</v>
+      </c>
+      <c r="G24">
+        <v>12600</v>
+      </c>
+      <c r="H24" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="I24" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24" t="str">
+        <v>提前还款，实还 12600 元超出应还 7000 元（合同标记提前结清）</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SPDB</v>
+      </c>
+      <c r="B25" t="str">
+        <v>AJ-2024-0004</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="str">
+        <v>early</v>
+      </c>
+      <c r="F25">
+        <v>7000</v>
+      </c>
+      <c r="G25">
+        <v>12600</v>
+      </c>
+      <c r="H25" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="I25" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25" t="str">
+        <v>提前还款，实还 12600 元超出应还 7000 元（合同标记提前结清）</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>ABC</v>
+      </c>
+      <c r="B26" t="str">
+        <v>AJ-2024-0004</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="str">
+        <v>early</v>
+      </c>
+      <c r="F26">
+        <v>7000</v>
+      </c>
+      <c r="G26">
+        <v>12600</v>
+      </c>
+      <c r="H26" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="I26" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26" t="str">
+        <v>提前还款，实还 12600 元超出应还 7000 元（合同标记提前结清）</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>COMM</v>
+      </c>
+      <c r="B27" t="str">
+        <v>AJ-2024-0004</v>
+      </c>
+      <c r="C27" t="str">
+        <v>赵六</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="str">
+        <v>early</v>
+      </c>
+      <c r="F27">
+        <v>7000</v>
+      </c>
+      <c r="G27">
+        <v>12600</v>
+      </c>
+      <c r="H27" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="I27" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27" t="str">
+        <v>提前还款，实还 12600 元超出应还 7000 元（合同标记提前结清）</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>CMB</v>
+      </c>
+      <c r="B28" t="str">
+        <v>AJ-2024-0004</v>
+      </c>
+      <c r="C28" t="str">
+        <v>赵六</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="str">
+        <v>early</v>
+      </c>
+      <c r="F28">
+        <v>7000</v>
+      </c>
+      <c r="G28">
+        <v>12600</v>
+      </c>
+      <c r="H28" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="I28" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28" t="str">
+        <v>提前还款，实还 12600 元超出应还 7000 元（合同标记提前结清）</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>ICBC</v>
+      </c>
+      <c r="B29" t="str">
+        <v>AJ-2024-0004</v>
+      </c>
+      <c r="C29" t="str">
+        <v>赵六</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="str">
+        <v>early</v>
+      </c>
+      <c r="F29">
+        <v>7000</v>
+      </c>
+      <c r="G29">
+        <v>12600</v>
+      </c>
+      <c r="H29" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="I29" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29" t="str">
+        <v>提前还款，实还 12600 元超出应还 7000 元（合同标记提前结清）</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>CCB</v>
+      </c>
+      <c r="B30" t="str">
+        <v>AJ-2024-0005</v>
+      </c>
+      <c r="C30" t="str">
+        <v>钱七</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30" t="str">
+        <v>rate_change</v>
+      </c>
+      <c r="F30">
+        <v>4400</v>
+      </c>
+      <c r="G30">
+        <v>4400</v>
+      </c>
+      <c r="H30" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I30" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30" t="str">
+        <v>利率调整：上期 3.25% 当期 3.5%</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>CMB</v>
+      </c>
+      <c r="B31" t="str">
+        <v>AJ-2024-0005</v>
+      </c>
+      <c r="C31" t="str">
+        <v>钱七</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" t="str">
+        <v>rate_change</v>
+      </c>
+      <c r="F31">
+        <v>4400</v>
+      </c>
+      <c r="G31">
+        <v>4400</v>
+      </c>
+      <c r="H31" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I31" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31" t="str">
+        <v>利率调整：上期 3.25% 当期 3.5%</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>ICBC</v>
+      </c>
+      <c r="B32" t="str">
+        <v>AJ-2024-0005</v>
+      </c>
+      <c r="C32" t="str">
+        <v>钱七</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32" t="str">
+        <v>rate_change</v>
+      </c>
+      <c r="F32">
+        <v>4400</v>
+      </c>
+      <c r="G32">
+        <v>4400</v>
+      </c>
+      <c r="H32" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I32" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32" t="str">
+        <v>利率调整：上期 3.25% 当期 3.5%</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>COMM</v>
+      </c>
+      <c r="B33" t="str">
+        <v>AJ-2024-0005</v>
+      </c>
+      <c r="C33" t="str">
+        <v>钱七</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33" t="str">
+        <v>rate_change</v>
+      </c>
+      <c r="F33">
+        <v>4400</v>
+      </c>
+      <c r="G33">
+        <v>4400</v>
+      </c>
+      <c r="H33" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I33" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33" t="str">
+        <v>利率调整：上期 3.25% 当期 3.5%</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>SPDB</v>
+      </c>
+      <c r="B34" t="str">
+        <v>AJ-2024-0005</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34" t="str">
+        <v>rate_change</v>
+      </c>
+      <c r="F34">
+        <v>4400</v>
+      </c>
+      <c r="G34">
+        <v>4400</v>
+      </c>
+      <c r="H34" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I34" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34" t="str">
+        <v>利率调整：上期 3.25% 当期 3.5%</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>ABC</v>
+      </c>
+      <c r="B35" t="str">
+        <v>AJ-2024-0005</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35" t="str">
+        <v>rate_change</v>
+      </c>
+      <c r="F35">
+        <v>4400</v>
+      </c>
+      <c r="G35">
+        <v>4400</v>
+      </c>
+      <c r="H35" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I35" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35" t="str">
+        <v>利率调整：上期 3.25% 当期 3.5%</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>CCB</v>
+      </c>
+      <c r="B36" t="str">
+        <v>AJ-2024-0007</v>
+      </c>
+      <c r="C36" t="str">
+        <v>周九</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F36">
+        <v>6100</v>
+      </c>
+      <c r="G36">
+        <v>6100</v>
+      </c>
+      <c r="H36" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="I36" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="J36">
+        <v>4</v>
+      </c>
+      <c r="K36">
+        <v>2.28</v>
+      </c>
+      <c r="L36" t="str">
+        <v>逾期 4 天，应还 6100 元，实还 6100 元，罚息 2.28 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>SPDB</v>
+      </c>
+      <c r="B37" t="str">
+        <v>AJ-2024-0007</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F37">
+        <v>6100</v>
+      </c>
+      <c r="G37">
+        <v>6100</v>
+      </c>
+      <c r="H37" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="I37" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="J37">
+        <v>4</v>
+      </c>
+      <c r="K37">
+        <v>2.28</v>
+      </c>
+      <c r="L37" t="str">
+        <v>逾期 4 天，应还 6100 元，实还 6100 元，罚息 2.28 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>ABC</v>
+      </c>
+      <c r="B38" t="str">
+        <v>AJ-2024-0007</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F38">
+        <v>6100</v>
+      </c>
+      <c r="G38">
+        <v>6100</v>
+      </c>
+      <c r="H38" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="I38" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="J38">
+        <v>4</v>
+      </c>
+      <c r="K38">
+        <v>2.28</v>
+      </c>
+      <c r="L38" t="str">
+        <v>逾期 4 天，应还 6100 元，实还 6100 元，罚息 2.28 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>COMM</v>
+      </c>
+      <c r="B39" t="str">
+        <v>AJ-2024-0007</v>
+      </c>
+      <c r="C39" t="str">
+        <v>周九</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F39">
+        <v>6100</v>
+      </c>
+      <c r="G39">
+        <v>6100</v>
+      </c>
+      <c r="H39" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="I39" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="J39">
+        <v>4</v>
+      </c>
+      <c r="K39">
+        <v>2.28</v>
+      </c>
+      <c r="L39" t="str">
+        <v>逾期 4 天，应还 6100 元，实还 6100 元，罚息 2.28 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>CMB</v>
+      </c>
+      <c r="B40" t="str">
+        <v>AJ-2024-0007</v>
+      </c>
+      <c r="C40" t="str">
+        <v>周九</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F40">
+        <v>6100</v>
+      </c>
+      <c r="G40">
+        <v>6100</v>
+      </c>
+      <c r="H40" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="I40" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="J40">
+        <v>4</v>
+      </c>
+      <c r="K40">
+        <v>2.28</v>
+      </c>
+      <c r="L40" t="str">
+        <v>逾期 4 天，应还 6100 元，实还 6100 元，罚息 2.28 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>ICBC</v>
+      </c>
+      <c r="B41" t="str">
+        <v>AJ-2024-0007</v>
+      </c>
+      <c r="C41" t="str">
+        <v>周九</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41" t="str">
+        <v>overdue</v>
+      </c>
+      <c r="F41">
+        <v>6100</v>
+      </c>
+      <c r="G41">
+        <v>6100</v>
+      </c>
+      <c r="H41" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="I41" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="J41">
+        <v>4</v>
+      </c>
+      <c r="K41">
+        <v>2.28</v>
+      </c>
+      <c r="L41" t="str">
+        <v>逾期 4 天，应还 6100 元，实还 6100 元，罚息 2.28 元（利率3.25%×1.5倍）</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>CCB</v>
+      </c>
+      <c r="B42" t="str">
+        <v>AJ-2024-0008</v>
+      </c>
+      <c r="C42" t="str">
+        <v>吴十</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42" t="str">
+        <v>unmatched</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42" t="str">
+        <v>未找到应还计划: 合同号=AJ-2024-0008 期次=1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>CMB</v>
+      </c>
+      <c r="B43" t="str">
+        <v>AJ-2024-0008</v>
+      </c>
+      <c r="C43" t="str">
+        <v>吴十</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="str">
+        <v>unmatched</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43" t="str">
+        <v>未找到应还计划: 合同号=AJ-2024-0008 期次=1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>ICBC</v>
+      </c>
+      <c r="B44" t="str">
+        <v>AJ-2024-0008</v>
+      </c>
+      <c r="C44" t="str">
+        <v>吴十</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="str">
+        <v>unmatched</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44" t="str">
+        <v>未找到应还计划: 合同号=AJ-2024-0008 期次=1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>COMM</v>
+      </c>
+      <c r="B45" t="str">
+        <v>AJ-2024-0008</v>
+      </c>
+      <c r="C45" t="str">
+        <v>吴十</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" t="str">
+        <v>unmatched</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45" t="str">
+        <v>未找到应还计划: 合同号=AJ-2024-0008 期次=1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>SPDB</v>
+      </c>
+      <c r="B46" t="str">
+        <v>AJ-2024-0008</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" t="str">
+        <v>unmatched</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46" t="str">
+        <v>未找到应还计划: 合同号=AJ-2024-0008 期次=1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>ABC</v>
+      </c>
+      <c r="B47" t="str">
+        <v>AJ-2024-0008</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47" t="str">
+        <v>unmatched</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47" t="str">
+        <v>未找到应还计划: 合同号=AJ-2024-0008 期次=1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L47"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -511,7 +2197,7 @@
         <v>114.75</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +2312,7 @@
         <v>114.75</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -638,7 +2324,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -682,31 +2368,31 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>部分还款笔数</v>
+        <v>逾期罚息合计_元</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>部分还款差额_元</v>
+        <v>部分还款笔数</v>
       </c>
       <c r="B7">
-        <v>1600</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>提前还款笔数</v>
+        <v>部分还款差额_元</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>利率调整笔数</v>
+        <v>提前还款笔数</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -714,23 +2400,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>未匹配笔数</v>
+        <v>利率调整笔数</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>未匹配笔数</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
         <v>统计月份</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B12" t="str">
         <v>2026-05</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
   </ignoredErrors>
 </worksheet>
 </file>